--- a/data/trans_orig/P32E$bar_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023</t>
+          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36895</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34700</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>23064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21649</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>23879</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20369</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>30884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>19537</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>82776</t>
+          <t>83638</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>106876</t>
+          <t>108288</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>122822</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>149033</t>
+          <t>150025</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>87186</t>
+          <t>87956</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>78322</t>
+          <t>79562</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>107576</t>
+          <t>109730</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23355</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>46973</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>58588</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>51410</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32E$bar_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>17006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30416</t>
+          <t>36528</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>43441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21097</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10838</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,27 +1329,27 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>35866</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>40852</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>19887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,27 +1898,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21588</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26320</t>
+          <t>28360</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23879</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>26719</t>
+          <t>28551</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>21839</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>33625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>26017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>671</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>21287</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>727</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,27 +3605,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>608</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>613</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -4252,27 +4252,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>610</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>610</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>83638</t>
+          <t>91893</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>117638</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>152399</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>122849</t>
+          <t>137276</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>150025</t>
+          <t>166546</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>72468</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>87956</t>
+          <t>100652</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>109790</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>79562</t>
+          <t>92920</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>109730</t>
+          <t>126553</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>39074</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>58588</t>
+          <t>70110</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>41745</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>53671</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -5160,32 +5160,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5195,32 +5195,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5230,32 +5230,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
